--- a/AAII_Financials/Yearly/NERV_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NERV_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="92">
   <si>
     <t>NERV</t>
   </si>
@@ -782,20 +782,20 @@
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
-        <v>5800</v>
-      </c>
-      <c r="E9" s="3">
-        <v>11900</v>
+      <c r="D9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F9" s="3">
         <v>12700</v>
       </c>
-      <c r="G9" s="3">
-        <v>14600</v>
-      </c>
-      <c r="H9" s="3">
-        <v>16800</v>
+      <c r="G9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I9" s="3">
         <v>22000</v>
@@ -833,20 +833,20 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="E10" s="3">
-        <v>-11900</v>
+      <c r="D10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F10" s="3">
         <v>-12700</v>
       </c>
-      <c r="G10" s="3">
-        <v>-14600</v>
-      </c>
-      <c r="H10" s="3">
-        <v>-16800</v>
+      <c r="G10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I10" s="3">
         <v>19100</v>
@@ -918,7 +918,7 @@
         <v>14600</v>
       </c>
       <c r="H12" s="3">
-        <v>32000</v>
+        <v>16800</v>
       </c>
       <c r="I12" s="3">
         <v>22000</v>
